--- a/outputs/395-36.xlsx
+++ b/outputs/395-36.xlsx
@@ -228,20 +228,24 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,53 +638,53 @@
   <dimension ref="A1:O15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1106,49 +1110,49 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1663,339 +1667,339 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="3" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="3" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="A6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="3" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="3" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="3" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="3" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="3" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="3" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="3" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="3" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="3" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="3" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="3" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="3" t="n">
         <v>535</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="3" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="3" t="n">
         <v>855</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/outputs/395-36.xlsx
+++ b/outputs/395-36.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Main unique ID" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Result what i am getting" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Result what i am expecting " sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="MyResult" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Result what i am getting'!$A$1:$O$1</definedName>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="27">
   <si>
     <t xml:space="preserve">Unique ID</t>
   </si>
@@ -635,7 +634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14.14"/>
@@ -1083,6 +1082,31 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
+        <v>500</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1">
@@ -1656,360 +1680,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>535</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>855</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>